--- a/tame_output/ON/bt/strategyON_20231217.xlsx
+++ b/tame_output/ON/bt/strategyON_20231217.xlsx
@@ -595,17 +595,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>86.6%</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-20.3%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -934,12 +934,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>488.2%</t>
+          <t>484.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-163.2%</t>
+          <t>-162.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-96.1%</t>
+          <t>-96.6%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1107,11 +1107,11 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2023-11-01</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1120,22 +1120,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-18.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>87.0%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1260,11 +1260,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-11-09</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1283,12 +1283,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1298,17 +1298,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-146.0%</t>
+          <t>-142.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-38.1%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.5%</t>
+          <t>112.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1413,11 +1413,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1431,17 +1431,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-10.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>110.7%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
     </row>
@@ -42197,7 +42197,7 @@
         <v>45231</v>
       </c>
       <c r="B1769" t="n">
-        <v>3.093259956227614</v>
+        <v>3.093259956227613</v>
       </c>
       <c r="C1769" t="n">
         <v>3.049962823512704</v>
@@ -42226,16 +42226,16 @@
         <v>3.048277258176837</v>
       </c>
       <c r="D1770" t="n">
-        <v>-2.853762907327241</v>
+        <v>-2.972340198271953</v>
       </c>
       <c r="E1770" t="n">
-        <v>1.906415670932194</v>
+        <v>1.858984754554309</v>
       </c>
       <c r="F1770" t="n">
-        <v>0.4528504876937213</v>
+        <v>0.3342731967490093</v>
       </c>
       <c r="G1770" t="n">
-        <v>3.319987550793071</v>
+        <v>3.248841176226244</v>
       </c>
     </row>
     <row r="1771">
@@ -42243,22 +42243,22 @@
         <v>45233</v>
       </c>
       <c r="B1771" t="n">
-        <v>3.069025022408317</v>
+        <v>3.069025022408316</v>
       </c>
       <c r="C1771" t="n">
         <v>3.051179068073428</v>
       </c>
       <c r="D1771" t="n">
-        <v>-2.854318662383279</v>
+        <v>-2.972895953327991</v>
       </c>
       <c r="E1771" t="n">
-        <v>1.90909517880637</v>
+        <v>1.861664262428485</v>
       </c>
       <c r="F1771" t="n">
-        <v>0.4512430739326433</v>
+        <v>0.3326657829879314</v>
       </c>
       <c r="G1771" t="n">
-        <v>3.321924912433016</v>
+        <v>3.250778537866188</v>
       </c>
     </row>
     <row r="1772">
@@ -42266,22 +42266,22 @@
         <v>45234</v>
       </c>
       <c r="B1772" t="n">
-        <v>3.085392865708495</v>
+        <v>3.085392865708494</v>
       </c>
       <c r="C1772" t="n">
         <v>3.056704057212575</v>
       </c>
       <c r="D1772" t="n">
-        <v>-2.85753301479659</v>
+        <v>-2.976110305741302</v>
       </c>
       <c r="E1772" t="n">
-        <v>1.913334426980192</v>
+        <v>1.865903510602307</v>
       </c>
       <c r="F1772" t="n">
-        <v>0.4512430739326433</v>
+        <v>0.3326657829879314</v>
       </c>
       <c r="G1772" t="n">
-        <v>3.327449901572163</v>
+        <v>3.256303527005335</v>
       </c>
     </row>
     <row r="1773">
@@ -42295,16 +42295,16 @@
         <v>3.057781629850306</v>
       </c>
       <c r="D1773" t="n">
-        <v>-2.874541260199199</v>
+        <v>-2.993118551143911</v>
       </c>
       <c r="E1773" t="n">
-        <v>1.90760870145688</v>
+        <v>1.860177785078995</v>
       </c>
       <c r="F1773" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3356649180009052</v>
       </c>
       <c r="G1773" t="n">
-        <v>3.330326955217679</v>
+        <v>3.259180580650851</v>
       </c>
     </row>
     <row r="1774">
@@ -42318,16 +42318,16 @@
         <v>3.058531492021579</v>
       </c>
       <c r="D1774" t="n">
-        <v>-2.855581537747845</v>
+        <v>-2.974158828692557</v>
       </c>
       <c r="E1774" t="n">
-        <v>1.915942452608694</v>
+        <v>1.86851153623081</v>
       </c>
       <c r="F1774" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3356649180009052</v>
       </c>
       <c r="G1774" t="n">
-        <v>3.331076817388952</v>
+        <v>3.259930442822124</v>
       </c>
     </row>
     <row r="1775">
@@ -42341,16 +42341,16 @@
         <v>3.05676708948516</v>
       </c>
       <c r="D1775" t="n">
-        <v>-2.854346813145036</v>
+        <v>-2.972924104089748</v>
       </c>
       <c r="E1775" t="n">
-        <v>1.914671939913399</v>
+        <v>1.867241023535514</v>
       </c>
       <c r="F1775" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3356649180009052</v>
       </c>
       <c r="G1775" t="n">
-        <v>3.329312414852533</v>
+        <v>3.258166040285705</v>
       </c>
     </row>
     <row r="1776">
@@ -42364,16 +42364,16 @@
         <v>3.060334699322022</v>
       </c>
       <c r="D1776" t="n">
-        <v>-2.864381076968685</v>
+        <v>-2.982958367913397</v>
       </c>
       <c r="E1776" t="n">
-        <v>1.914225844220801</v>
+        <v>1.866794927842917</v>
       </c>
       <c r="F1776" t="n">
-        <v>0.4542422089456171</v>
+        <v>0.3356649180009052</v>
       </c>
       <c r="G1776" t="n">
-        <v>3.332880024689394</v>
+        <v>3.261733650122567</v>
       </c>
     </row>
     <row r="1777">
@@ -42387,16 +42387,16 @@
         <v>3.084316661211631</v>
       </c>
       <c r="D1777" t="n">
-        <v>-2.869420075266552</v>
+        <v>-2.987997366211264</v>
       </c>
       <c r="E1777" t="n">
-        <v>1.936192206791264</v>
+        <v>1.888761290413379</v>
       </c>
       <c r="F1777" t="n">
-        <v>0.4492032106477504</v>
+        <v>0.3306259197030385</v>
       </c>
       <c r="G1777" t="n">
-        <v>3.353838587600283</v>
+        <v>3.282692213033456</v>
       </c>
     </row>
     <row r="1778">
@@ -42410,16 +42410,16 @@
         <v>3.081785372698861</v>
       </c>
       <c r="D1778" t="n">
-        <v>-2.859600357106001</v>
+        <v>-2.978177648050713</v>
       </c>
       <c r="E1778" t="n">
-        <v>1.937588805542714</v>
+        <v>1.890157889164829</v>
       </c>
       <c r="F1778" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3370558599197259</v>
       </c>
       <c r="G1778" t="n">
-        <v>3.355165263217525</v>
+        <v>3.284018888650698</v>
       </c>
     </row>
     <row r="1779">
@@ -42433,16 +42433,16 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-2.857798730267047</v>
+        <v>-2.976376021211759</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.923558018281921</v>
+        <v>1.876127101904036</v>
       </c>
       <c r="F1779" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3370558599197259</v>
       </c>
       <c r="G1779" t="n">
-        <v>3.340413825221151</v>
+        <v>3.269267450654324</v>
       </c>
     </row>
     <row r="1780">
@@ -42456,16 +42456,16 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-2.856810048522879</v>
+        <v>-2.975387339467591</v>
       </c>
       <c r="E1780" t="n">
-        <v>1.92206724729526</v>
+        <v>1.874636330917375</v>
       </c>
       <c r="F1780" t="n">
-        <v>0.4556331508644378</v>
+        <v>0.3370558599197259</v>
       </c>
       <c r="G1780" t="n">
-        <v>3.338527581536823</v>
+        <v>3.267381206969996</v>
       </c>
     </row>
     <row r="1781">
@@ -42479,16 +42479,16 @@
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-2.848813694001341</v>
+        <v>-2.967390984946053</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.927239415559716</v>
+        <v>1.879808499181831</v>
       </c>
       <c r="F1781" t="n">
-        <v>0.4636295053859764</v>
+        <v>0.3450522144412644</v>
       </c>
       <c r="G1781" t="n">
-        <v>3.345299020705586</v>
+        <v>3.274152646138759</v>
       </c>
     </row>
     <row r="1782">
@@ -42502,16 +42502,16 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-2.843829943329432</v>
+        <v>-2.962407234274144</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.941071496419391</v>
+        <v>1.893640580041506</v>
       </c>
       <c r="F1782" t="n">
-        <v>0.4686132560578851</v>
+        <v>0.3500359651131731</v>
       </c>
       <c r="G1782" t="n">
-        <v>3.360127851699644</v>
+        <v>3.288981477132816</v>
       </c>
     </row>
     <row r="1783">
@@ -42525,16 +42525,16 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-2.837443804379876</v>
+        <v>-2.956021095324588</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.950354155011003</v>
+        <v>1.902923238633117</v>
       </c>
       <c r="F1783" t="n">
-        <v>0.4686132560578851</v>
+        <v>0.3500359651131731</v>
       </c>
       <c r="G1783" t="n">
-        <v>3.366856054711433</v>
+        <v>3.295709680144605</v>
       </c>
     </row>
     <row r="1784">
@@ -42548,16 +42548,16 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-2.849249154698509</v>
+        <v>-2.967826445643221</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.949648103643092</v>
+        <v>1.902217187265207</v>
       </c>
       <c r="F1784" t="n">
-        <v>0.4568079057392525</v>
+        <v>0.3382306147945405</v>
       </c>
       <c r="G1784" t="n">
-        <v>3.363788933279795</v>
+        <v>3.292642558712968</v>
       </c>
     </row>
     <row r="1785">
@@ -42571,16 +42571,16 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-2.840517343919843</v>
+        <v>-2.959094634864555</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.959088285564448</v>
+        <v>1.911657369186563</v>
       </c>
       <c r="F1785" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3469624255732068</v>
       </c>
       <c r="G1785" t="n">
-        <v>3.374975477356884</v>
+        <v>3.303829102790057</v>
       </c>
     </row>
     <row r="1786">
@@ -42594,16 +42594,16 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-2.834180457275391</v>
+        <v>-2.952757748220103</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.956933859170214</v>
+        <v>1.909502942792329</v>
       </c>
       <c r="F1786" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3469624255732068</v>
       </c>
       <c r="G1786" t="n">
-        <v>3.37028629630487</v>
+        <v>3.299139921738043</v>
       </c>
     </row>
     <row r="1787">
@@ -42617,16 +42617,16 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-2.831646009548022</v>
+        <v>-2.950223300492735</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.967910296063355</v>
+        <v>1.92047937968547</v>
       </c>
       <c r="F1787" t="n">
-        <v>0.4655397165179187</v>
+        <v>0.3469624255732068</v>
       </c>
       <c r="G1787" t="n">
-        <v>3.380248954107063</v>
+        <v>3.309102579540236</v>
       </c>
     </row>
     <row r="1788">
@@ -42640,16 +42640,16 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-2.831721908528627</v>
+        <v>-2.950299199473339</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.960294616664023</v>
+        <v>1.912863700286138</v>
       </c>
       <c r="F1788" t="n">
-        <v>0.4663029772072456</v>
+        <v>0.3477256862625336</v>
       </c>
       <c r="G1788" t="n">
-        <v>3.373121590713569</v>
+        <v>3.301975216146742</v>
       </c>
     </row>
     <row r="1789">
@@ -42663,16 +42663,16 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-2.842224098087974</v>
+        <v>-2.960801389032686</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.933858316630657</v>
+        <v>1.886427400252773</v>
       </c>
       <c r="F1789" t="n">
-        <v>0.4558007876478989</v>
+        <v>0.337223496703187</v>
       </c>
       <c r="G1789" t="n">
-        <v>3.344584852768335</v>
+        <v>3.273438478201507</v>
       </c>
     </row>
     <row r="1790">
@@ -42680,22 +42680,22 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.146053372487811</v>
+        <v>3.14605337248781</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-2.84405736076709</v>
+        <v>-2.962634651711802</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.933825851405132</v>
+        <v>1.886394935027248</v>
       </c>
       <c r="F1790" t="n">
-        <v>0.4558007876478989</v>
+        <v>0.337223496703187</v>
       </c>
       <c r="G1790" t="n">
-        <v>3.345285692614457</v>
+        <v>3.274139318047629</v>
       </c>
     </row>
     <row r="1791">
@@ -42709,16 +42709,16 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-2.849066475828674</v>
+        <v>-2.967643766773386</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.932339285209359</v>
+        <v>1.884908368831474</v>
       </c>
       <c r="F1791" t="n">
-        <v>0.4548062100893642</v>
+        <v>0.3362289191446523</v>
       </c>
       <c r="G1791" t="n">
-        <v>3.345206025908195</v>
+        <v>3.274059651341368</v>
       </c>
     </row>
     <row r="1792">
@@ -42732,16 +42732,16 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-2.852772032465488</v>
+        <v>-2.9713493234102</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.930084787794998</v>
+        <v>1.882653871417113</v>
       </c>
       <c r="F1792" t="n">
-        <v>0.4529365348317293</v>
+        <v>0.3343592438870174</v>
       </c>
       <c r="G1792" t="n">
-        <v>3.34331194599398</v>
+        <v>3.272165571427152</v>
       </c>
     </row>
     <row r="1793">
@@ -42755,16 +42755,16 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-2.851539707108123</v>
+        <v>-2.970116998052835</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.930997570000264</v>
+        <v>1.883566653622379</v>
       </c>
       <c r="F1793" t="n">
-        <v>0.4535669112037669</v>
+        <v>0.3349896202590549</v>
       </c>
       <c r="G1793" t="n">
-        <v>3.344110023879521</v>
+        <v>3.272963649312694</v>
       </c>
     </row>
     <row r="1794">
@@ -42772,22 +42772,22 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714843</v>
+        <v>3.147014107714844</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-2.841211710092271</v>
+        <v>-2.959789001036983</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.939258676970818</v>
+        <v>1.891827760592933</v>
       </c>
       <c r="F1794" t="n">
-        <v>0.463894908219619</v>
+        <v>0.3453176172749071</v>
       </c>
       <c r="G1794" t="n">
-        <v>3.354436730253246</v>
+        <v>3.283290355686419</v>
       </c>
     </row>
     <row r="1795">
@@ -42795,22 +42795,22 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083876</v>
+        <v>3.136752015083877</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-2.841095374944715</v>
+        <v>-2.959672665889427</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.945825871231677</v>
+        <v>1.898394954853792</v>
       </c>
       <c r="F1795" t="n">
-        <v>0.4640112433671748</v>
+        <v>0.3454339524224628</v>
       </c>
       <c r="G1795" t="n">
-        <v>3.361027191543616</v>
+        <v>3.289880816976789</v>
       </c>
     </row>
     <row r="1796">
@@ -42818,22 +42818,22 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666733</v>
+        <v>3.162269743666734</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-2.842940784521582</v>
+        <v>-2.961518075466294</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.942061677846318</v>
+        <v>1.894630761468433</v>
       </c>
       <c r="F1796" t="n">
-        <v>0.4640112433671748</v>
+        <v>0.3454339524224628</v>
       </c>
       <c r="G1796" t="n">
-        <v>3.358001161989004</v>
+        <v>3.286854787422177</v>
       </c>
     </row>
     <row r="1797">
@@ -42841,22 +42841,22 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097098</v>
+        <v>3.163432091097099</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-2.841442351996483</v>
+        <v>-2.960019642941195</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.942599338717491</v>
+        <v>1.895168422339606</v>
       </c>
       <c r="F1797" t="n">
-        <v>0.4655096758922737</v>
+        <v>0.3469323849475617</v>
       </c>
       <c r="G1797" t="n">
-        <v>3.358838509365197</v>
+        <v>3.28769213479837</v>
       </c>
     </row>
     <row r="1798">
@@ -42864,22 +42864,22 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762258</v>
+        <v>3.169279212762259</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-2.849506604189217</v>
+        <v>-2.968083895133929</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.940651615783709</v>
+        <v>1.893220699405824</v>
       </c>
       <c r="F1798" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3388681327548279</v>
       </c>
       <c r="G1798" t="n">
-        <v>3.355277935992869</v>
+        <v>3.284131561426041</v>
       </c>
     </row>
     <row r="1799">
@@ -42887,22 +42887,22 @@
         <v>45261</v>
       </c>
       <c r="B1799" t="n">
-        <v>3.185514355963479</v>
+        <v>3.18551435596348</v>
       </c>
       <c r="C1799" t="n">
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-2.850836571650429</v>
+        <v>-2.969413862595141</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.940119628799224</v>
+        <v>1.89268871242134</v>
       </c>
       <c r="F1799" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3388681327548279</v>
       </c>
       <c r="G1799" t="n">
-        <v>3.355277935992869</v>
+        <v>3.284131561426041</v>
       </c>
     </row>
     <row r="1800">
@@ -42910,22 +42910,22 @@
         <v>45262</v>
       </c>
       <c r="B1800" t="n">
-        <v>3.199276732583694</v>
+        <v>3.199276732583695</v>
       </c>
       <c r="C1800" t="n">
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-2.622971888916918</v>
+        <v>-2.74154917986163</v>
       </c>
       <c r="E1800" t="n">
-        <v>2.033481974999791</v>
+        <v>1.986051058621906</v>
       </c>
       <c r="F1800" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3388681327548279</v>
       </c>
       <c r="G1800" t="n">
-        <v>3.357494409100031</v>
+        <v>3.286348034533203</v>
       </c>
     </row>
     <row r="1801">
@@ -42933,22 +42933,22 @@
         <v>45263</v>
       </c>
       <c r="B1801" t="n">
-        <v>3.238767863742724</v>
+        <v>3.238767863742725</v>
       </c>
       <c r="C1801" t="n">
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.374870325049701</v>
+        <v>-2.493447615994413</v>
       </c>
       <c r="E1801" t="n">
-        <v>2.14025719689177</v>
+        <v>2.092826280513885</v>
       </c>
       <c r="F1801" t="n">
-        <v>0.4574454236995398</v>
+        <v>0.3388681327548279</v>
       </c>
       <c r="G1801" t="n">
-        <v>3.365029005445123</v>
+        <v>3.293882630878295</v>
       </c>
     </row>
     <row r="1802">
@@ -42956,22 +42956,22 @@
         <v>45264</v>
       </c>
       <c r="B1802" t="n">
-        <v>3.260068416589524</v>
+        <v>3.260068416589525</v>
       </c>
       <c r="C1802" t="n">
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.078031925656371</v>
+        <v>-2.196609216601083</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.260415567622559</v>
+        <v>2.212984651244675</v>
       </c>
       <c r="F1802" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4537226212359556</v>
       </c>
       <c r="G1802" t="n">
-        <v>3.435364709507257</v>
+        <v>3.36421833494043</v>
       </c>
     </row>
     <row r="1803">
@@ -42979,22 +42979,22 @@
         <v>45265</v>
       </c>
       <c r="B1803" t="n">
-        <v>3.306739876872957</v>
+        <v>3.306739876872958</v>
       </c>
       <c r="C1803" t="n">
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-1.774392368830935</v>
+        <v>-1.892969659775647</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.38354846481842</v>
+        <v>2.336117548440536</v>
       </c>
       <c r="F1803" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4537226212359556</v>
       </c>
       <c r="G1803" t="n">
-        <v>3.437041783972943</v>
+        <v>3.365895409406116</v>
       </c>
     </row>
     <row r="1804">
@@ -43002,22 +43002,22 @@
         <v>45266</v>
       </c>
       <c r="B1804" t="n">
-        <v>3.312164595946329</v>
+        <v>3.31216459594633</v>
       </c>
       <c r="C1804" t="n">
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.485371762390226</v>
+        <v>-1.603949053334938</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.495096128844161</v>
+        <v>2.447665212466277</v>
       </c>
       <c r="F1804" t="n">
-        <v>0.5722999121806676</v>
+        <v>0.4537226212359556</v>
       </c>
       <c r="G1804" t="n">
-        <v>3.432981205422401</v>
+        <v>3.361834830855574</v>
       </c>
     </row>
     <row r="1805">
@@ -43031,16 +43031,16 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.200651835126329</v>
+        <v>-1.319229126071041</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.614204239093738</v>
+        <v>2.566773322715853</v>
       </c>
       <c r="F1805" t="n">
-        <v>0.8570198394445647</v>
+        <v>0.7384425484998527</v>
       </c>
       <c r="G1805" t="n">
-        <v>3.609033301124757</v>
+        <v>3.537886926557929</v>
       </c>
     </row>
     <row r="1806">
@@ -43048,22 +43048,22 @@
         <v>45268</v>
       </c>
       <c r="B1806" t="n">
-        <v>3.318449829143339</v>
+        <v>3.31844982914334</v>
       </c>
       <c r="C1806" t="n">
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-0.9168901656347888</v>
+        <v>-1.035467456579501</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.733021070064161</v>
+        <v>2.685590153686276</v>
       </c>
       <c r="F1806" t="n">
-        <v>0.8570198394445647</v>
+        <v>0.7384425484998527</v>
       </c>
       <c r="G1806" t="n">
-        <v>3.614345464298564</v>
+        <v>3.543199089731736</v>
       </c>
     </row>
     <row r="1807">
@@ -43071,22 +43071,22 @@
         <v>45269</v>
       </c>
       <c r="B1807" t="n">
-        <v>3.311781349308503</v>
+        <v>3.311781349308504</v>
       </c>
       <c r="C1807" t="n">
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-0.6552417712421481</v>
+        <v>-0.7738190621868601</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.830923015267851</v>
+        <v>2.783492098889966</v>
       </c>
       <c r="F1807" t="n">
-        <v>1.118668233837205</v>
+        <v>1.000090942892493</v>
       </c>
       <c r="G1807" t="n">
-        <v>3.764577088380782</v>
+        <v>3.693430713813954</v>
       </c>
     </row>
     <row r="1808">
@@ -43094,22 +43094,22 @@
         <v>45270</v>
       </c>
       <c r="B1808" t="n">
-        <v>3.271427670257516</v>
+        <v>3.271427670257517</v>
       </c>
       <c r="C1808" t="n">
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.3410753331028157</v>
+        <v>-0.4596526240475277</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.954053265539696</v>
+        <v>2.906622349161812</v>
       </c>
       <c r="F1808" t="n">
-        <v>1.432834671976538</v>
+        <v>1.314257381031826</v>
       </c>
       <c r="G1808" t="n">
-        <v>3.950540626280493</v>
+        <v>3.879394251713666</v>
       </c>
     </row>
     <row r="1809">
@@ -43117,22 +43117,22 @@
         <v>45271</v>
       </c>
       <c r="B1809" t="n">
-        <v>3.25296238744154</v>
+        <v>3.252962387441541</v>
       </c>
       <c r="C1809" t="n">
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.2185636289970433</v>
+        <v>-0.3371409199417553</v>
       </c>
       <c r="E1809" t="n">
-        <v>3.021472330808745</v>
+        <v>2.97404141443086</v>
       </c>
       <c r="F1809" t="n">
-        <v>1.55534637608231</v>
+        <v>1.436769085137598</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.042462032370696</v>
+        <v>3.971315657803869</v>
       </c>
     </row>
     <row r="1810">
@@ -43140,22 +43140,22 @@
         <v>45272</v>
       </c>
       <c r="B1810" t="n">
-        <v>3.241257540662168</v>
+        <v>3.241257540662169</v>
       </c>
       <c r="C1810" t="n">
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.05717509507031493</v>
+        <v>-0.175752386015027</v>
       </c>
       <c r="E1810" t="n">
-        <v>3.095843868434915</v>
+        <v>3.04841295205703</v>
       </c>
       <c r="F1810" t="n">
-        <v>1.716734910009039</v>
+        <v>1.598157619064327</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.149111276782212</v>
+        <v>4.077964902215385</v>
       </c>
     </row>
     <row r="1811">
@@ -43163,22 +43163,22 @@
         <v>45273</v>
       </c>
       <c r="B1811" t="n">
-        <v>3.285495323543324</v>
+        <v>3.285495323543325</v>
       </c>
       <c r="C1811" t="n">
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>0.1225710960781913</v>
+        <v>0.003993805133479245</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.181269956946248</v>
+        <v>3.133839040568364</v>
       </c>
       <c r="F1811" t="n">
-        <v>1.716734910009039</v>
+        <v>1.598157619064327</v>
       </c>
       <c r="G1811" t="n">
-        <v>4.162638888834143</v>
+        <v>4.091492514267316</v>
       </c>
     </row>
     <row r="1812">
@@ -43186,22 +43186,22 @@
         <v>45274</v>
       </c>
       <c r="B1812" t="n">
-        <v>3.287726162978608</v>
+        <v>3.287726162978609</v>
       </c>
       <c r="C1812" t="n">
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>0.2813720225494142</v>
+        <v>0.1627947316047021</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.251377707786003</v>
+        <v>3.203946791408118</v>
       </c>
       <c r="F1812" t="n">
-        <v>1.716734910009039</v>
+        <v>1.598157619064327</v>
       </c>
       <c r="G1812" t="n">
-        <v>4.169226269085409</v>
+        <v>4.098079894518582</v>
       </c>
     </row>
     <row r="1813">
@@ -43209,22 +43209,22 @@
         <v>45275</v>
       </c>
       <c r="B1813" t="n">
-        <v>3.275586179621267</v>
+        <v>3.275586179621268</v>
       </c>
       <c r="C1813" t="n">
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>0.374160480854791</v>
+        <v>0.255583189910079</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.277403839542861</v>
+        <v>3.229972923164976</v>
       </c>
       <c r="F1813" t="n">
-        <v>1.809523368314415</v>
+        <v>1.690946077369703</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.213810092503341</v>
+        <v>4.142663717936514</v>
       </c>
     </row>
     <row r="1814">
@@ -43232,22 +43232,22 @@
         <v>45276</v>
       </c>
       <c r="B1814" t="n">
-        <v>3.113249472436856</v>
+        <v>3.101901745056636</v>
       </c>
       <c r="C1814" t="n">
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.4635010679182385</v>
+        <v>0.4583523710216267</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.308740571878964</v>
+        <v>3.306681093120319</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.818423923703016</v>
+        <v>1.712042896032738</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.214750923247226</v>
+        <v>4.150922306645059</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231217.xlsx
+++ b/tame_output/ON/bt/strategyON_20231217.xlsx
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-96.6%</t>
+          <t>-96.5%</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
     </row>
@@ -42220,7 +42220,7 @@
         <v>45232</v>
       </c>
       <c r="B1770" t="n">
-        <v>3.06824651857159</v>
+        <v>3.068246518571589</v>
       </c>
       <c r="C1770" t="n">
         <v>3.048277258176837</v>
@@ -42312,7 +42312,7 @@
         <v>45236</v>
       </c>
       <c r="B1774" t="n">
-        <v>3.074518669066013</v>
+        <v>3.074518669066012</v>
       </c>
       <c r="C1774" t="n">
         <v>3.058531492021579</v>
@@ -42335,7 +42335,7 @@
         <v>45237</v>
       </c>
       <c r="B1775" t="n">
-        <v>3.087505451293022</v>
+        <v>3.087505451293021</v>
       </c>
       <c r="C1775" t="n">
         <v>3.05676708948516</v>
@@ -42358,7 +42358,7 @@
         <v>45238</v>
       </c>
       <c r="B1776" t="n">
-        <v>3.125945945239775</v>
+        <v>3.125945945239774</v>
       </c>
       <c r="C1776" t="n">
         <v>3.060334699322022</v>
@@ -42404,7 +42404,7 @@
         <v>45240</v>
       </c>
       <c r="B1778" t="n">
-        <v>3.135555340167862</v>
+        <v>3.135555340167861</v>
       </c>
       <c r="C1778" t="n">
         <v>3.081785372698861</v>
@@ -42427,7 +42427,7 @@
         <v>45241</v>
       </c>
       <c r="B1779" t="n">
-        <v>3.134141625216943</v>
+        <v>3.134141625216942</v>
       </c>
       <c r="C1779" t="n">
         <v>3.067033934702486</v>
@@ -42450,7 +42450,7 @@
         <v>45242</v>
       </c>
       <c r="B1780" t="n">
-        <v>3.132018996454039</v>
+        <v>3.132018996454038</v>
       </c>
       <c r="C1780" t="n">
         <v>3.065147691018159</v>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780868</v>
+        <v>3.120443325780867</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42496,7 +42496,7 @@
         <v>45244</v>
       </c>
       <c r="B1782" t="n">
-        <v>3.095206606537931</v>
+        <v>3.09520660653793</v>
       </c>
       <c r="C1782" t="n">
         <v>3.078959898064911</v>
@@ -42519,7 +42519,7 @@
         <v>45245</v>
       </c>
       <c r="B1783" t="n">
-        <v>3.147410092597767</v>
+        <v>3.147410092597766</v>
       </c>
       <c r="C1783" t="n">
         <v>3.0856881010767</v>
@@ -42542,7 +42542,7 @@
         <v>45246</v>
       </c>
       <c r="B1784" t="n">
-        <v>3.120684616527686</v>
+        <v>3.120684616527685</v>
       </c>
       <c r="C1784" t="n">
         <v>3.089704189836242</v>
@@ -42565,7 +42565,7 @@
         <v>45247</v>
       </c>
       <c r="B1785" t="n">
-        <v>3.118866618844645</v>
+        <v>3.118866618844644</v>
       </c>
       <c r="C1785" t="n">
         <v>3.095651647446132</v>
@@ -42611,7 +42611,7 @@
         <v>45249</v>
       </c>
       <c r="B1787" t="n">
-        <v>3.141819250502548</v>
+        <v>3.141819250502547</v>
       </c>
       <c r="C1787" t="n">
         <v>3.100925124196311</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728031</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42657,7 +42657,7 @@
         <v>45251</v>
       </c>
       <c r="B1789" t="n">
-        <v>3.120735995702055</v>
+        <v>3.120735995702054</v>
       </c>
       <c r="C1789" t="n">
         <v>3.071104380179594</v>
@@ -42680,7 +42680,7 @@
         <v>45252</v>
       </c>
       <c r="B1790" t="n">
-        <v>3.14605337248781</v>
+        <v>3.146053372487809</v>
       </c>
       <c r="C1790" t="n">
         <v>3.071805220025715</v>
@@ -42703,7 +42703,7 @@
         <v>45253</v>
       </c>
       <c r="B1791" t="n">
-        <v>3.146265744823381</v>
+        <v>3.14626574482338</v>
       </c>
       <c r="C1791" t="n">
         <v>3.072322299854575</v>
@@ -42726,7 +42726,7 @@
         <v>45254</v>
       </c>
       <c r="B1792" t="n">
-        <v>3.157777201524822</v>
+        <v>3.157777201524821</v>
       </c>
       <c r="C1792" t="n">
         <v>3.07155002509494</v>
@@ -42749,7 +42749,7 @@
         <v>45255</v>
       </c>
       <c r="B1793" t="n">
-        <v>3.157294380068702</v>
+        <v>3.157294380068701</v>
       </c>
       <c r="C1793" t="n">
         <v>3.071969877157259</v>
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.147014107714844</v>
+        <v>3.147014107714843</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42795,7 +42795,7 @@
         <v>45257</v>
       </c>
       <c r="B1795" t="n">
-        <v>3.136752015083877</v>
+        <v>3.136752015083876</v>
       </c>
       <c r="C1795" t="n">
         <v>3.082620445523309</v>
@@ -42818,7 +42818,7 @@
         <v>45258</v>
       </c>
       <c r="B1796" t="n">
-        <v>3.162269743666734</v>
+        <v>3.162269743666733</v>
       </c>
       <c r="C1796" t="n">
         <v>3.079594415968698</v>
@@ -42841,7 +42841,7 @@
         <v>45259</v>
       </c>
       <c r="B1797" t="n">
-        <v>3.163432091097099</v>
+        <v>3.163432091097098</v>
       </c>
       <c r="C1797" t="n">
         <v>3.079532703829831</v>
@@ -42864,7 +42864,7 @@
         <v>45260</v>
       </c>
       <c r="B1798" t="n">
-        <v>3.169279212762259</v>
+        <v>3.169279212762258</v>
       </c>
       <c r="C1798" t="n">
         <v>3.080810681773143</v>
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.4583523710216267</v>
+        <v>0.4590002304785995</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.306681093120319</v>
+        <v>3.306940236903108</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.712042896032738</v>
+        <v>1.712070548478604</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.150922306645059</v>
+        <v>4.150938898112579</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231217.xlsx
+++ b/tame_output/ON/bt/strategyON_20231217.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>484.2%</t>
+          <t>481.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-96.5%</t>
+          <t>-107.5%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1145,27 +1145,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-16.1%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-38.1%</t>
+          <t>-39.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.7%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -43238,16 +43238,16 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.4590002304785995</v>
+        <v>0.3496036852809209</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.306940236903108</v>
+        <v>3.263181618824037</v>
       </c>
       <c r="F1814" t="n">
-        <v>1.712070548478604</v>
+        <v>1.700788517862687</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.150938898112579</v>
+        <v>4.144169679743029</v>
       </c>
     </row>
   </sheetData>
